--- a/data/historial/2026-08-05.xlsx
+++ b/data/historial/2026-08-05.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Desktop\Reportes Ventas Rap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C0EF7F84-E923-4BFF-939C-BF51A4308DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8BE020-79CA-4477-A102-39B3092465B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -940,7 +940,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
@@ -949,7 +949,6 @@
     <numFmt numFmtId="167" formatCode="&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.000;\-#,##0.000"/>
     <numFmt numFmtId="169" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -2056,7 +2055,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2302,7 +2301,6 @@
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="18" fillId="34" borderId="25" xfId="47" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2819,1198 +2817,1198 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="152" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="153" t="s">
+      <c r="B1" s="152" t="s">
         <v>146</v>
       </c>
-      <c r="C1" s="153" t="s">
+      <c r="C1" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="153" t="s">
+      <c r="D1" s="152" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="153" t="s">
+      <c r="E1" s="152" t="s">
         <v>149</v>
       </c>
-      <c r="F1" s="153" t="s">
+      <c r="F1" s="152" t="s">
         <v>150</v>
       </c>
-      <c r="G1" s="153" t="s">
+      <c r="G1" s="152" t="s">
         <v>151</v>
       </c>
-      <c r="H1" s="153" t="s">
+      <c r="H1" s="152" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="152" t="s">
+      <c r="A2" s="151" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="152">
-        <v>0</v>
-      </c>
-      <c r="C2" s="152">
+      <c r="B2" s="151">
+        <v>0</v>
+      </c>
+      <c r="C2" s="151">
         <v>14088.7310059473</v>
       </c>
-      <c r="D2" s="152">
+      <c r="D2" s="151">
         <v>61315.230254553797</v>
       </c>
-      <c r="E2" s="152">
+      <c r="E2" s="151">
         <v>254996298.9447462</v>
       </c>
-      <c r="F2" s="152">
-        <v>0</v>
-      </c>
-      <c r="G2" s="152">
+      <c r="F2" s="151">
+        <v>0</v>
+      </c>
+      <c r="G2" s="151">
         <v>134107.436028378</v>
       </c>
-      <c r="H2" s="152">
+      <c r="H2" s="151">
         <v>134107.51</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="152" t="s">
+      <c r="A3" s="151" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="152">
+      <c r="B3" s="151">
         <v>1</v>
       </c>
-      <c r="C3" s="152">
+      <c r="C3" s="151">
         <v>182.58883928489999</v>
       </c>
-      <c r="D3" s="152">
+      <c r="D3" s="151">
         <v>352.62731398950001</v>
       </c>
-      <c r="E3" s="152">
+      <c r="E3" s="151">
         <v>4470247.8676125938</v>
       </c>
-      <c r="F3" s="152">
-        <v>0</v>
-      </c>
-      <c r="G3" s="152">
+      <c r="F3" s="151">
+        <v>0</v>
+      </c>
+      <c r="G3" s="151">
         <v>134107.436028378</v>
       </c>
-      <c r="H3" s="152">
+      <c r="H3" s="151">
         <v>134107.51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="152" t="s">
+      <c r="A4" s="151" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="152">
+      <c r="B4" s="151">
         <v>1</v>
       </c>
-      <c r="C4" s="152">
+      <c r="C4" s="151">
         <v>151.7062500001</v>
       </c>
-      <c r="D4" s="152">
+      <c r="D4" s="151">
         <v>163.02375000519999</v>
       </c>
-      <c r="E4" s="152">
+      <c r="E4" s="151">
         <v>2927957.2046600222</v>
       </c>
-      <c r="F4" s="152">
-        <v>0</v>
-      </c>
-      <c r="G4" s="152">
-        <v>0</v>
-      </c>
-      <c r="H4" s="152">
+      <c r="F4" s="151">
+        <v>0</v>
+      </c>
+      <c r="G4" s="151">
+        <v>0</v>
+      </c>
+      <c r="H4" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="152" t="s">
+      <c r="A5" s="151" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="152">
+      <c r="B5" s="151">
         <v>1</v>
       </c>
-      <c r="C5" s="152">
+      <c r="C5" s="151">
         <v>166.32093253849999</v>
       </c>
-      <c r="D5" s="152">
+      <c r="D5" s="151">
         <v>474.07267856980002</v>
       </c>
-      <c r="E5" s="152">
+      <c r="E5" s="151">
         <v>4631927.624667611</v>
       </c>
-      <c r="F5" s="152">
-        <v>0</v>
-      </c>
-      <c r="G5" s="152">
-        <v>0</v>
-      </c>
-      <c r="H5" s="152">
+      <c r="F5" s="151">
+        <v>0</v>
+      </c>
+      <c r="G5" s="151">
+        <v>0</v>
+      </c>
+      <c r="H5" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="151" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="152">
+      <c r="B6" s="151">
         <v>1</v>
       </c>
-      <c r="C6" s="152">
+      <c r="C6" s="151">
         <v>266.26299603159998</v>
       </c>
-      <c r="D6" s="152">
+      <c r="D6" s="151">
         <v>473.71785714549998</v>
       </c>
-      <c r="E6" s="152">
+      <c r="E6" s="151">
         <v>6392972.1405321835</v>
       </c>
-      <c r="F6" s="152">
-        <v>0</v>
-      </c>
-      <c r="G6" s="152">
-        <v>0</v>
-      </c>
-      <c r="H6" s="152">
+      <c r="F6" s="151">
+        <v>0</v>
+      </c>
+      <c r="G6" s="151">
+        <v>0</v>
+      </c>
+      <c r="H6" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="152" t="s">
+      <c r="A7" s="151" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="152">
+      <c r="B7" s="151">
         <v>1</v>
       </c>
-      <c r="C7" s="152">
+      <c r="C7" s="151">
         <v>217.8493452381</v>
       </c>
-      <c r="D7" s="152">
+      <c r="D7" s="151">
         <v>544.90416668360001</v>
       </c>
-      <c r="E7" s="152">
+      <c r="E7" s="151">
         <v>4272340.5982830664</v>
       </c>
-      <c r="F7" s="152">
-        <v>0</v>
-      </c>
-      <c r="G7" s="152">
-        <v>0</v>
-      </c>
-      <c r="H7" s="152">
+      <c r="F7" s="151">
+        <v>0</v>
+      </c>
+      <c r="G7" s="151">
+        <v>0</v>
+      </c>
+      <c r="H7" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="151" t="s">
         <v>110</v>
       </c>
-      <c r="B8" s="152">
+      <c r="B8" s="151">
         <v>1</v>
       </c>
-      <c r="C8" s="152">
+      <c r="C8" s="151">
         <v>417.9166666667</v>
       </c>
-      <c r="D8" s="152">
+      <c r="D8" s="151">
         <v>1344.2700000003999</v>
       </c>
-      <c r="E8" s="152">
+      <c r="E8" s="151">
         <v>13846941.29303805</v>
       </c>
-      <c r="F8" s="152">
-        <v>0</v>
-      </c>
-      <c r="G8" s="152">
-        <v>0</v>
-      </c>
-      <c r="H8" s="152">
+      <c r="F8" s="151">
+        <v>0</v>
+      </c>
+      <c r="G8" s="151">
+        <v>0</v>
+      </c>
+      <c r="H8" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="152" t="s">
+      <c r="A9" s="151" t="s">
         <v>269</v>
       </c>
-      <c r="B9" s="152">
+      <c r="B9" s="151">
         <v>1</v>
       </c>
-      <c r="C9" s="152">
+      <c r="C9" s="151">
         <v>139.34474206339999</v>
       </c>
-      <c r="D9" s="152">
+      <c r="D9" s="151">
         <v>386.36375000430002</v>
       </c>
-      <c r="E9" s="152">
+      <c r="E9" s="151">
         <v>2955434.4121029563</v>
       </c>
-      <c r="F9" s="152">
-        <v>0</v>
-      </c>
-      <c r="G9" s="152">
-        <v>0</v>
-      </c>
-      <c r="H9" s="152">
+      <c r="F9" s="151">
+        <v>0</v>
+      </c>
+      <c r="G9" s="151">
+        <v>0</v>
+      </c>
+      <c r="H9" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="152">
+      <c r="B10" s="151">
         <v>1</v>
       </c>
-      <c r="C10" s="152">
+      <c r="C10" s="151">
         <v>124.1674007938</v>
       </c>
-      <c r="D10" s="152">
+      <c r="D10" s="151">
         <v>212.79173810219999</v>
       </c>
-      <c r="E10" s="152">
+      <c r="E10" s="151">
         <v>2922050.7653640723</v>
       </c>
-      <c r="F10" s="152">
-        <v>0</v>
-      </c>
-      <c r="G10" s="152">
-        <v>0</v>
-      </c>
-      <c r="H10" s="152">
+      <c r="F10" s="151">
+        <v>0</v>
+      </c>
+      <c r="G10" s="151">
+        <v>0</v>
+      </c>
+      <c r="H10" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="152" t="s">
+      <c r="A11" s="151" t="s">
         <v>210</v>
       </c>
-      <c r="B11" s="152">
+      <c r="B11" s="151">
         <v>1</v>
       </c>
-      <c r="C11" s="152">
+      <c r="C11" s="151">
         <v>123.6425595237</v>
       </c>
-      <c r="D11" s="152">
+      <c r="D11" s="151">
         <v>160.3147619101</v>
       </c>
-      <c r="E11" s="152">
+      <c r="E11" s="151">
         <v>2458105.1791371955</v>
       </c>
-      <c r="F11" s="152">
-        <v>0</v>
-      </c>
-      <c r="G11" s="152">
-        <v>0</v>
-      </c>
-      <c r="H11" s="152">
+      <c r="F11" s="151">
+        <v>0</v>
+      </c>
+      <c r="G11" s="151">
+        <v>0</v>
+      </c>
+      <c r="H11" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="152" t="s">
+      <c r="A12" s="151" t="s">
         <v>209</v>
       </c>
-      <c r="B12" s="152">
+      <c r="B12" s="151">
         <v>1</v>
       </c>
-      <c r="C12" s="152">
+      <c r="C12" s="151">
         <v>179.6415079363</v>
       </c>
-      <c r="D12" s="152">
+      <c r="D12" s="151">
         <v>316.26250000319999</v>
       </c>
-      <c r="E12" s="152">
+      <c r="E12" s="151">
         <v>3238435.7546853684</v>
       </c>
-      <c r="F12" s="152">
-        <v>0</v>
-      </c>
-      <c r="G12" s="152">
-        <v>0</v>
-      </c>
-      <c r="H12" s="152">
+      <c r="F12" s="151">
+        <v>0</v>
+      </c>
+      <c r="G12" s="151">
+        <v>0</v>
+      </c>
+      <c r="H12" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="152" t="s">
+      <c r="A13" s="151" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="152">
+      <c r="B13" s="151">
         <v>1</v>
       </c>
-      <c r="C13" s="152">
+      <c r="C13" s="151">
         <v>151.54533730130001</v>
       </c>
-      <c r="D13" s="152">
+      <c r="D13" s="151">
         <v>573.89410714320002</v>
       </c>
-      <c r="E13" s="152">
+      <c r="E13" s="151">
         <v>3837107.6640388942</v>
       </c>
-      <c r="F13" s="152">
-        <v>0</v>
-      </c>
-      <c r="G13" s="152">
-        <v>0</v>
-      </c>
-      <c r="H13" s="152">
+      <c r="F13" s="151">
+        <v>0</v>
+      </c>
+      <c r="G13" s="151">
+        <v>0</v>
+      </c>
+      <c r="H13" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="152" t="s">
+      <c r="A14" s="151" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="152">
+      <c r="B14" s="151">
         <v>1</v>
       </c>
-      <c r="C14" s="152">
+      <c r="C14" s="151">
         <v>769.51309523819998</v>
       </c>
-      <c r="D14" s="152">
+      <c r="D14" s="151">
         <v>2602.7242857127999</v>
       </c>
-      <c r="E14" s="152">
+      <c r="E14" s="151">
         <v>12112146.959749941</v>
       </c>
-      <c r="F14" s="152">
-        <v>0</v>
-      </c>
-      <c r="G14" s="152">
-        <v>0</v>
-      </c>
-      <c r="H14" s="152">
+      <c r="F14" s="151">
+        <v>0</v>
+      </c>
+      <c r="G14" s="151">
+        <v>0</v>
+      </c>
+      <c r="H14" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="152" t="s">
+      <c r="A15" s="151" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="152">
+      <c r="B15" s="151">
         <v>1</v>
       </c>
-      <c r="C15" s="152">
+      <c r="C15" s="151">
         <v>160.89700793700001</v>
       </c>
-      <c r="D15" s="152">
+      <c r="D15" s="151">
         <v>406.99541666729999</v>
       </c>
-      <c r="E15" s="152">
+      <c r="E15" s="151">
         <v>3228302.1331991754</v>
       </c>
-      <c r="F15" s="152">
-        <v>0</v>
-      </c>
-      <c r="G15" s="152">
-        <v>0</v>
-      </c>
-      <c r="H15" s="152">
+      <c r="F15" s="151">
+        <v>0</v>
+      </c>
+      <c r="G15" s="151">
+        <v>0</v>
+      </c>
+      <c r="H15" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="152" t="s">
+      <c r="A16" s="151" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="152">
+      <c r="B16" s="151">
         <v>1</v>
       </c>
-      <c r="C16" s="152">
+      <c r="C16" s="151">
         <v>123.5364682534</v>
       </c>
-      <c r="D16" s="152">
+      <c r="D16" s="151">
         <v>454.79500000439998</v>
       </c>
-      <c r="E16" s="152">
+      <c r="E16" s="151">
         <v>3640196.5802759319</v>
       </c>
-      <c r="F16" s="152">
-        <v>0</v>
-      </c>
-      <c r="G16" s="152">
-        <v>0</v>
-      </c>
-      <c r="H16" s="152">
+      <c r="F16" s="151">
+        <v>0</v>
+      </c>
+      <c r="G16" s="151">
+        <v>0</v>
+      </c>
+      <c r="H16" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="152" t="s">
+      <c r="A17" s="151" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="152">
+      <c r="B17" s="151">
         <v>1</v>
       </c>
-      <c r="C17" s="152">
+      <c r="C17" s="151">
         <v>239.8317063488</v>
       </c>
-      <c r="D17" s="152">
+      <c r="D17" s="151">
         <v>701.89651190990003</v>
       </c>
-      <c r="E17" s="152">
+      <c r="E17" s="151">
         <v>5484537.3014732655</v>
       </c>
-      <c r="F17" s="152">
-        <v>0</v>
-      </c>
-      <c r="G17" s="152">
-        <v>0</v>
-      </c>
-      <c r="H17" s="152">
+      <c r="F17" s="151">
+        <v>0</v>
+      </c>
+      <c r="G17" s="151">
+        <v>0</v>
+      </c>
+      <c r="H17" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="152" t="s">
+      <c r="A18" s="151" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="152">
+      <c r="B18" s="151">
         <v>1</v>
       </c>
-      <c r="C18" s="152">
+      <c r="C18" s="151">
         <v>437.43617063490001</v>
       </c>
-      <c r="D18" s="152">
+      <c r="D18" s="151">
         <v>1055.2479166659</v>
       </c>
-      <c r="E18" s="152">
+      <c r="E18" s="151">
         <v>8033782.2496290058</v>
       </c>
-      <c r="F18" s="152">
-        <v>0</v>
-      </c>
-      <c r="G18" s="152">
-        <v>0</v>
-      </c>
-      <c r="H18" s="152">
+      <c r="F18" s="151">
+        <v>0</v>
+      </c>
+      <c r="G18" s="151">
+        <v>0</v>
+      </c>
+      <c r="H18" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="152" t="s">
+      <c r="A19" s="151" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="152">
+      <c r="B19" s="151">
         <v>1</v>
       </c>
-      <c r="C19" s="152">
+      <c r="C19" s="151">
         <v>295.50611772500002</v>
       </c>
-      <c r="D19" s="152">
+      <c r="D19" s="151">
         <v>702.32749999819998</v>
       </c>
-      <c r="E19" s="152">
+      <c r="E19" s="151">
         <v>6285739.3230815595</v>
       </c>
-      <c r="F19" s="152">
-        <v>0</v>
-      </c>
-      <c r="G19" s="152">
-        <v>0</v>
-      </c>
-      <c r="H19" s="152">
+      <c r="F19" s="151">
+        <v>0</v>
+      </c>
+      <c r="G19" s="151">
+        <v>0</v>
+      </c>
+      <c r="H19" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="151" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="152">
+      <c r="B20" s="151">
         <v>1</v>
       </c>
-      <c r="C20" s="152">
+      <c r="C20" s="151">
         <v>1528.4662698411</v>
       </c>
-      <c r="D20" s="152">
+      <c r="D20" s="151">
         <v>2792.7997619038001</v>
       </c>
-      <c r="E20" s="152">
+      <c r="E20" s="151">
         <v>19809972.012772713</v>
       </c>
-      <c r="F20" s="152">
-        <v>0</v>
-      </c>
-      <c r="G20" s="152">
-        <v>0</v>
-      </c>
-      <c r="H20" s="152">
+      <c r="F20" s="151">
+        <v>0</v>
+      </c>
+      <c r="G20" s="151">
+        <v>0</v>
+      </c>
+      <c r="H20" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="152" t="s">
+      <c r="A21" s="151" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="152">
+      <c r="B21" s="151">
         <v>1</v>
       </c>
-      <c r="C21" s="152">
+      <c r="C21" s="151">
         <v>151.99654761880001</v>
       </c>
-      <c r="D21" s="152">
+      <c r="D21" s="151">
         <v>496.68850000729998</v>
       </c>
-      <c r="E21" s="152">
+      <c r="E21" s="151">
         <v>3499843.0210882789</v>
       </c>
-      <c r="F21" s="152">
-        <v>0</v>
-      </c>
-      <c r="G21" s="152">
-        <v>0</v>
-      </c>
-      <c r="H21" s="152">
+      <c r="F21" s="151">
+        <v>0</v>
+      </c>
+      <c r="G21" s="151">
+        <v>0</v>
+      </c>
+      <c r="H21" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="151" t="s">
         <v>274</v>
       </c>
-      <c r="B22" s="152">
+      <c r="B22" s="151">
         <v>1</v>
       </c>
-      <c r="C22" s="152">
+      <c r="C22" s="151">
         <v>128.14228174569999</v>
       </c>
-      <c r="D22" s="152">
+      <c r="D22" s="151">
         <v>279.01125000270002</v>
       </c>
-      <c r="E22" s="152">
+      <c r="E22" s="151">
         <v>3185102.5027717678</v>
       </c>
-      <c r="F22" s="152">
-        <v>0</v>
-      </c>
-      <c r="G22" s="152">
-        <v>0</v>
-      </c>
-      <c r="H22" s="152">
+      <c r="F22" s="151">
+        <v>0</v>
+      </c>
+      <c r="G22" s="151">
+        <v>0</v>
+      </c>
+      <c r="H22" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="152" t="s">
+      <c r="A23" s="151" t="s">
         <v>266</v>
       </c>
-      <c r="B23" s="152">
+      <c r="B23" s="151">
         <v>1</v>
       </c>
-      <c r="C23" s="152">
+      <c r="C23" s="151">
         <v>114.88833333319999</v>
       </c>
-      <c r="D23" s="152">
+      <c r="D23" s="151">
         <v>261.0049999986</v>
       </c>
-      <c r="E23" s="152">
+      <c r="E23" s="151">
         <v>2923678.1117493762</v>
       </c>
-      <c r="F23" s="152">
-        <v>0</v>
-      </c>
-      <c r="G23" s="152">
-        <v>0</v>
-      </c>
-      <c r="H23" s="152">
+      <c r="F23" s="151">
+        <v>0</v>
+      </c>
+      <c r="G23" s="151">
+        <v>0</v>
+      </c>
+      <c r="H23" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="152" t="s">
+      <c r="A24" s="151" t="s">
         <v>265</v>
       </c>
-      <c r="B24" s="152">
+      <c r="B24" s="151">
         <v>1</v>
       </c>
-      <c r="C24" s="152">
+      <c r="C24" s="151">
         <v>1186.2236111113</v>
       </c>
-      <c r="D24" s="152">
+      <c r="D24" s="151">
         <v>9813.7326071470998</v>
       </c>
-      <c r="E24" s="152">
+      <c r="E24" s="151">
         <v>24101898.667897765</v>
       </c>
-      <c r="F24" s="152">
-        <v>0</v>
-      </c>
-      <c r="G24" s="152">
-        <v>0</v>
-      </c>
-      <c r="H24" s="152">
+      <c r="F24" s="151">
+        <v>0</v>
+      </c>
+      <c r="G24" s="151">
+        <v>0</v>
+      </c>
+      <c r="H24" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="152" t="s">
+      <c r="A25" s="151" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="152">
+      <c r="B25" s="151">
         <v>1</v>
       </c>
-      <c r="C25" s="152">
+      <c r="C25" s="151">
         <v>93.241170635000003</v>
       </c>
-      <c r="D25" s="152">
+      <c r="D25" s="151">
         <v>385.96458333869998</v>
       </c>
-      <c r="E25" s="152">
+      <c r="E25" s="151">
         <v>2335213.6486873631</v>
       </c>
-      <c r="F25" s="152">
-        <v>0</v>
-      </c>
-      <c r="G25" s="152">
-        <v>0</v>
-      </c>
-      <c r="H25" s="152">
+      <c r="F25" s="151">
+        <v>0</v>
+      </c>
+      <c r="G25" s="151">
+        <v>0</v>
+      </c>
+      <c r="H25" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="152" t="s">
+      <c r="A26" s="151" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="152">
+      <c r="B26" s="151">
         <v>1</v>
       </c>
-      <c r="C26" s="152">
+      <c r="C26" s="151">
         <v>126.4617063491</v>
       </c>
-      <c r="D26" s="152">
+      <c r="D26" s="151">
         <v>181.13066666360001</v>
       </c>
-      <c r="E26" s="152">
+      <c r="E26" s="151">
         <v>2515670.4237700473</v>
       </c>
-      <c r="F26" s="152">
-        <v>0</v>
-      </c>
-      <c r="G26" s="152">
-        <v>0</v>
-      </c>
-      <c r="H26" s="152">
+      <c r="F26" s="151">
+        <v>0</v>
+      </c>
+      <c r="G26" s="151">
+        <v>0</v>
+      </c>
+      <c r="H26" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="152" t="s">
+      <c r="A27" s="151" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="152">
+      <c r="B27" s="151">
         <v>1</v>
       </c>
-      <c r="C27" s="152">
+      <c r="C27" s="151">
         <v>329.2916666667</v>
       </c>
-      <c r="D27" s="152">
+      <c r="D27" s="151">
         <v>2898.94</v>
       </c>
-      <c r="E27" s="152">
+      <c r="E27" s="151">
         <v>5512726.2555622831</v>
       </c>
-      <c r="F27" s="152">
-        <v>0</v>
-      </c>
-      <c r="G27" s="152">
-        <v>0</v>
-      </c>
-      <c r="H27" s="152">
+      <c r="F27" s="151">
+        <v>0</v>
+      </c>
+      <c r="G27" s="151">
+        <v>0</v>
+      </c>
+      <c r="H27" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="152" t="s">
+      <c r="A28" s="151" t="s">
         <v>218</v>
       </c>
-      <c r="B28" s="152">
+      <c r="B28" s="151">
         <v>1</v>
       </c>
-      <c r="C28" s="152">
+      <c r="C28" s="151">
         <v>184.35212301589999</v>
       </c>
-      <c r="D28" s="152">
+      <c r="D28" s="151">
         <v>539.30392857490006</v>
       </c>
-      <c r="E28" s="152">
+      <c r="E28" s="151">
         <v>3897878.0298985899</v>
       </c>
-      <c r="F28" s="152">
-        <v>0</v>
-      </c>
-      <c r="G28" s="152">
-        <v>0</v>
-      </c>
-      <c r="H28" s="152">
+      <c r="F28" s="151">
+        <v>0</v>
+      </c>
+      <c r="G28" s="151">
+        <v>0</v>
+      </c>
+      <c r="H28" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="152" t="s">
+      <c r="A29" s="151" t="s">
         <v>211</v>
       </c>
-      <c r="B29" s="152">
+      <c r="B29" s="151">
         <v>1</v>
       </c>
-      <c r="C29" s="152">
+      <c r="C29" s="151">
         <v>252.46679894159999</v>
       </c>
-      <c r="D29" s="152">
+      <c r="D29" s="151">
         <v>903.01285714309995</v>
       </c>
-      <c r="E29" s="152">
+      <c r="E29" s="151">
         <v>4826567.6426148191</v>
       </c>
-      <c r="F29" s="152">
-        <v>0</v>
-      </c>
-      <c r="G29" s="152">
-        <v>0</v>
-      </c>
-      <c r="H29" s="152">
+      <c r="F29" s="151">
+        <v>0</v>
+      </c>
+      <c r="G29" s="151">
+        <v>0</v>
+      </c>
+      <c r="H29" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="152" t="s">
+      <c r="A30" s="151" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="152">
+      <c r="B30" s="151">
         <v>1</v>
       </c>
-      <c r="C30" s="152">
+      <c r="C30" s="151">
         <v>87.584722221700005</v>
       </c>
-      <c r="D30" s="152">
+      <c r="D30" s="151">
         <v>137.51500000120001</v>
       </c>
-      <c r="E30" s="152">
+      <c r="E30" s="151">
         <v>1773841.7023678774</v>
       </c>
-      <c r="F30" s="152">
-        <v>0</v>
-      </c>
-      <c r="G30" s="152">
-        <v>0</v>
-      </c>
-      <c r="H30" s="152">
+      <c r="F30" s="151">
+        <v>0</v>
+      </c>
+      <c r="G30" s="151">
+        <v>0</v>
+      </c>
+      <c r="H30" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="152" t="s">
+      <c r="A31" s="151" t="s">
         <v>213</v>
       </c>
-      <c r="B31" s="152">
+      <c r="B31" s="151">
         <v>1</v>
       </c>
-      <c r="C31" s="152">
+      <c r="C31" s="151">
         <v>175.828571428</v>
       </c>
-      <c r="D31" s="152">
+      <c r="D31" s="151">
         <v>308.40708333510003</v>
       </c>
-      <c r="E31" s="152">
+      <c r="E31" s="151">
         <v>2870562.2247181726</v>
       </c>
-      <c r="F31" s="152">
-        <v>0</v>
-      </c>
-      <c r="G31" s="152">
-        <v>0</v>
-      </c>
-      <c r="H31" s="152">
+      <c r="F31" s="151">
+        <v>0</v>
+      </c>
+      <c r="G31" s="151">
+        <v>0</v>
+      </c>
+      <c r="H31" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="152" t="s">
+      <c r="A32" s="151" t="s">
         <v>272</v>
       </c>
-      <c r="B32" s="152">
+      <c r="B32" s="151">
         <v>1</v>
       </c>
-      <c r="C32" s="152">
+      <c r="C32" s="151">
         <v>171.75853174560001</v>
       </c>
-      <c r="D32" s="152">
+      <c r="D32" s="151">
         <v>59.010000000799998</v>
       </c>
-      <c r="E32" s="152">
+      <c r="E32" s="151">
         <v>2452499.2938377094</v>
       </c>
-      <c r="F32" s="152">
-        <v>0</v>
-      </c>
-      <c r="G32" s="152">
-        <v>0</v>
-      </c>
-      <c r="H32" s="152">
+      <c r="F32" s="151">
+        <v>0</v>
+      </c>
+      <c r="G32" s="151">
+        <v>0</v>
+      </c>
+      <c r="H32" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="152" t="s">
+      <c r="A33" s="151" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="152">
+      <c r="B33" s="151">
         <v>1</v>
       </c>
-      <c r="C33" s="152">
+      <c r="C33" s="151">
         <v>204.1220634922</v>
       </c>
-      <c r="D33" s="152">
+      <c r="D33" s="151">
         <v>805.78916666780003</v>
       </c>
-      <c r="E33" s="152">
+      <c r="E33" s="151">
         <v>3887629.4191952711</v>
       </c>
-      <c r="F33" s="152">
-        <v>0</v>
-      </c>
-      <c r="G33" s="152">
-        <v>0</v>
-      </c>
-      <c r="H33" s="152">
+      <c r="F33" s="151">
+        <v>0</v>
+      </c>
+      <c r="G33" s="151">
+        <v>0</v>
+      </c>
+      <c r="H33" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="152" t="s">
+      <c r="A34" s="151" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="152">
+      <c r="B34" s="151">
         <v>1</v>
       </c>
-      <c r="C34" s="152">
+      <c r="C34" s="151">
         <v>208.45833333339999</v>
       </c>
-      <c r="D34" s="152">
+      <c r="D34" s="151">
         <v>1299.8599999999999</v>
       </c>
-      <c r="E34" s="152">
+      <c r="E34" s="151">
         <v>3242995.6574940565</v>
       </c>
-      <c r="F34" s="152">
-        <v>0</v>
-      </c>
-      <c r="G34" s="152">
-        <v>0</v>
-      </c>
-      <c r="H34" s="152">
+      <c r="F34" s="151">
+        <v>0</v>
+      </c>
+      <c r="G34" s="151">
+        <v>0</v>
+      </c>
+      <c r="H34" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="152" t="s">
+      <c r="A35" s="151" t="s">
         <v>160</v>
       </c>
-      <c r="B35" s="152">
+      <c r="B35" s="151">
         <v>1</v>
       </c>
-      <c r="C35" s="152">
+      <c r="C35" s="151">
         <v>103.5329365074</v>
       </c>
-      <c r="D35" s="152">
+      <c r="D35" s="151">
         <v>335.10125000490001</v>
       </c>
-      <c r="E35" s="152">
+      <c r="E35" s="151">
         <v>2545958.7967660916</v>
       </c>
-      <c r="F35" s="152">
-        <v>0</v>
-      </c>
-      <c r="G35" s="152">
-        <v>0</v>
-      </c>
-      <c r="H35" s="152">
+      <c r="F35" s="151">
+        <v>0</v>
+      </c>
+      <c r="G35" s="151">
+        <v>0</v>
+      </c>
+      <c r="H35" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="152" t="s">
+      <c r="A36" s="151" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="152">
+      <c r="B36" s="151">
         <v>1</v>
       </c>
-      <c r="C36" s="152">
+      <c r="C36" s="151">
         <v>366.04799603200001</v>
       </c>
-      <c r="D36" s="152">
+      <c r="D36" s="151">
         <v>1960.6685833337001</v>
       </c>
-      <c r="E36" s="152">
+      <c r="E36" s="151">
         <v>10375630.87772402</v>
       </c>
-      <c r="F36" s="152">
-        <v>0</v>
-      </c>
-      <c r="G36" s="152">
-        <v>0</v>
-      </c>
-      <c r="H36" s="152">
+      <c r="F36" s="151">
+        <v>0</v>
+      </c>
+      <c r="G36" s="151">
+        <v>0</v>
+      </c>
+      <c r="H36" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="152" t="s">
+      <c r="A37" s="151" t="s">
         <v>270</v>
       </c>
-      <c r="B37" s="152">
+      <c r="B37" s="151">
         <v>1</v>
       </c>
-      <c r="C37" s="152">
+      <c r="C37" s="151">
         <v>419.70833333320002</v>
       </c>
-      <c r="D37" s="152">
+      <c r="D37" s="151">
         <v>4805.0399999990004</v>
       </c>
-      <c r="E37" s="152">
+      <c r="E37" s="151">
         <v>10542806.037602939</v>
       </c>
-      <c r="F37" s="152">
-        <v>0</v>
-      </c>
-      <c r="G37" s="152">
-        <v>0</v>
-      </c>
-      <c r="H37" s="152">
+      <c r="F37" s="151">
+        <v>0</v>
+      </c>
+      <c r="G37" s="151">
+        <v>0</v>
+      </c>
+      <c r="H37" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="152" t="s">
+      <c r="A38" s="151" t="s">
         <v>107</v>
       </c>
-      <c r="B38" s="152">
+      <c r="B38" s="151">
         <v>1</v>
       </c>
-      <c r="C38" s="152">
+      <c r="C38" s="151">
         <v>292.66666666660001</v>
       </c>
-      <c r="D38" s="152">
+      <c r="D38" s="151">
         <v>3446.3999999988</v>
       </c>
-      <c r="E38" s="152">
+      <c r="E38" s="151">
         <v>6793509.4167299801</v>
       </c>
-      <c r="F38" s="152">
-        <v>0</v>
-      </c>
-      <c r="G38" s="152">
-        <v>0</v>
-      </c>
-      <c r="H38" s="152">
+      <c r="F38" s="151">
+        <v>0</v>
+      </c>
+      <c r="G38" s="151">
+        <v>0</v>
+      </c>
+      <c r="H38" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="152" t="s">
+      <c r="A39" s="151" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="152">
+      <c r="B39" s="151">
         <v>1</v>
       </c>
-      <c r="C39" s="152">
+      <c r="C39" s="151">
         <v>115.05357142840001</v>
       </c>
-      <c r="D39" s="152">
+      <c r="D39" s="151">
         <v>336.30267857339999</v>
       </c>
-      <c r="E39" s="152">
+      <c r="E39" s="151">
         <v>3261064.8254967621</v>
       </c>
-      <c r="F39" s="152">
-        <v>0</v>
-      </c>
-      <c r="G39" s="152">
-        <v>0</v>
-      </c>
-      <c r="H39" s="152">
+      <c r="F39" s="151">
+        <v>0</v>
+      </c>
+      <c r="G39" s="151">
+        <v>0</v>
+      </c>
+      <c r="H39" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="152" t="s">
+      <c r="A40" s="151" t="s">
         <v>139</v>
       </c>
-      <c r="B40" s="152">
+      <c r="B40" s="151">
         <v>1</v>
       </c>
-      <c r="C40" s="152">
+      <c r="C40" s="151">
         <v>2631.9859126983001</v>
       </c>
-      <c r="D40" s="152">
+      <c r="D40" s="151">
         <v>10359.0116666666</v>
       </c>
-      <c r="E40" s="152">
+      <c r="E40" s="151">
         <v>21705529.123024561</v>
       </c>
-      <c r="F40" s="152">
-        <v>0</v>
-      </c>
-      <c r="G40" s="152">
-        <v>0</v>
-      </c>
-      <c r="H40" s="152">
+      <c r="F40" s="151">
+        <v>0</v>
+      </c>
+      <c r="G40" s="151">
+        <v>0</v>
+      </c>
+      <c r="H40" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="152" t="s">
+      <c r="A41" s="151" t="s">
         <v>284</v>
       </c>
-      <c r="B41" s="152">
+      <c r="B41" s="151">
         <v>1</v>
       </c>
-      <c r="C41" s="152">
+      <c r="C41" s="151">
         <v>236</v>
       </c>
-      <c r="D41" s="152">
+      <c r="D41" s="151">
         <v>2922.32</v>
       </c>
-      <c r="E41" s="152">
+      <c r="E41" s="151">
         <v>6114784.5568000004</v>
       </c>
-      <c r="F41" s="152">
-        <v>0</v>
-      </c>
-      <c r="G41" s="152">
-        <v>0</v>
-      </c>
-      <c r="H41" s="152">
+      <c r="F41" s="151">
+        <v>0</v>
+      </c>
+      <c r="G41" s="151">
+        <v>0</v>
+      </c>
+      <c r="H41" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="152" t="s">
+      <c r="A42" s="151" t="s">
         <v>144</v>
       </c>
-      <c r="B42" s="152">
+      <c r="B42" s="151">
         <v>1</v>
       </c>
-      <c r="C42" s="152">
+      <c r="C42" s="151">
         <v>127.9555555556</v>
       </c>
-      <c r="D42" s="152">
+      <c r="D42" s="151">
         <v>615.17583333410005</v>
       </c>
-      <c r="E42" s="152">
+      <c r="E42" s="151">
         <v>2847535.638590497</v>
       </c>
-      <c r="F42" s="152">
-        <v>0</v>
-      </c>
-      <c r="G42" s="152">
-        <v>0</v>
-      </c>
-      <c r="H42" s="152">
+      <c r="F42" s="151">
+        <v>0</v>
+      </c>
+      <c r="G42" s="151">
+        <v>0</v>
+      </c>
+      <c r="H42" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="152" t="s">
+      <c r="A43" s="151" t="s">
         <v>145</v>
       </c>
-      <c r="B43" s="152">
+      <c r="B43" s="151">
         <v>1</v>
       </c>
-      <c r="C43" s="152">
+      <c r="C43" s="151">
         <v>-2.4583333333000001</v>
       </c>
-      <c r="D43" s="152">
-        <v>0</v>
-      </c>
-      <c r="E43" s="152">
+      <c r="D43" s="151">
+        <v>0</v>
+      </c>
+      <c r="E43" s="151">
         <v>-80990.517827873206</v>
       </c>
-      <c r="F43" s="152">
-        <v>0</v>
-      </c>
-      <c r="G43" s="152">
-        <v>0</v>
-      </c>
-      <c r="H43" s="152">
+      <c r="F43" s="151">
+        <v>0</v>
+      </c>
+      <c r="G43" s="151">
+        <v>0</v>
+      </c>
+      <c r="H43" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="152" t="s">
+      <c r="A44" s="151" t="s">
         <v>273</v>
       </c>
-      <c r="B44" s="152">
+      <c r="B44" s="151">
         <v>1</v>
       </c>
-      <c r="C44" s="152">
+      <c r="C44" s="151">
         <v>367.08511904739998</v>
       </c>
-      <c r="D44" s="152">
+      <c r="D44" s="151">
         <v>807.91058333449996</v>
       </c>
-      <c r="E44" s="152">
+      <c r="E44" s="151">
         <v>7269845.9948500441</v>
       </c>
-      <c r="F44" s="152">
-        <v>0</v>
-      </c>
-      <c r="G44" s="152">
-        <v>0</v>
-      </c>
-      <c r="H44" s="152">
+      <c r="F44" s="151">
+        <v>0</v>
+      </c>
+      <c r="G44" s="151">
+        <v>0</v>
+      </c>
+      <c r="H44" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="152" t="s">
+      <c r="A45" s="151" t="s">
         <v>154</v>
       </c>
-      <c r="B45" s="152">
+      <c r="B45" s="151">
         <v>1</v>
       </c>
-      <c r="C45" s="152">
+      <c r="C45" s="151">
         <v>96.849484127799997</v>
       </c>
-      <c r="D45" s="152">
+      <c r="D45" s="151">
         <v>733.90000000860005</v>
       </c>
-      <c r="E45" s="152">
+      <c r="E45" s="151">
         <v>2220501.5457263547</v>
       </c>
-      <c r="F45" s="152">
-        <v>0</v>
-      </c>
-      <c r="G45" s="152">
-        <v>0</v>
-      </c>
-      <c r="H45" s="152">
+      <c r="F45" s="151">
+        <v>0</v>
+      </c>
+      <c r="G45" s="151">
+        <v>0</v>
+      </c>
+      <c r="H45" s="151">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="152" t="s">
+      <c r="A46" s="151" t="s">
         <v>217</v>
       </c>
-      <c r="B46" s="152">
+      <c r="B46" s="151">
         <v>1</v>
       </c>
-      <c r="C46" s="152">
+      <c r="C46" s="151">
         <v>243.31388888890001</v>
       </c>
-      <c r="D46" s="152">
+      <c r="D46" s="151">
         <v>2905</v>
       </c>
-      <c r="E46" s="152">
+      <c r="E46" s="151">
         <v>3825818.9833058524</v>
       </c>
-      <c r="F46" s="152">
-        <v>0</v>
-      </c>
-      <c r="G46" s="152">
-        <v>0</v>
-      </c>
-      <c r="H46" s="152">
+      <c r="F46" s="151">
+        <v>0</v>
+      </c>
+      <c r="G46" s="151">
+        <v>0</v>
+      </c>
+      <c r="H46" s="151">
         <v>0</v>
       </c>
     </row>
@@ -9345,7 +9343,7 @@
       <c r="L2" s="103">
         <v>907871.92636018235</v>
       </c>
-      <c r="N2" s="150" t="s">
+      <c r="N2" s="149" t="s">
         <v>37</v>
       </c>
       <c r="O2">
@@ -9408,7 +9406,7 @@
       <c r="L3" s="105">
         <v>707919.37019508681</v>
       </c>
-      <c r="N3" s="150"/>
+      <c r="N3" s="149"/>
       <c r="O3">
         <v>49</v>
       </c>
@@ -9469,7 +9467,7 @@
       <c r="L4" s="105">
         <v>276942.08389738784</v>
       </c>
-      <c r="N4" s="150"/>
+      <c r="N4" s="149"/>
       <c r="O4">
         <v>20</v>
       </c>
@@ -9530,7 +9528,7 @@
       <c r="L5" s="105">
         <v>699165.05217344186</v>
       </c>
-      <c r="N5" s="150"/>
+      <c r="N5" s="149"/>
       <c r="O5">
         <v>15</v>
       </c>
@@ -9591,7 +9589,7 @@
       <c r="L6" s="105">
         <v>0</v>
       </c>
-      <c r="N6" s="150"/>
+      <c r="N6" s="149"/>
       <c r="O6">
         <v>19</v>
       </c>
@@ -9652,7 +9650,7 @@
       <c r="L7" s="105">
         <v>265320.43464193383</v>
       </c>
-      <c r="N7" s="150"/>
+      <c r="N7" s="149"/>
       <c r="O7">
         <v>16</v>
       </c>
@@ -9713,7 +9711,7 @@
       <c r="L8" s="105">
         <v>454186.93616588484</v>
       </c>
-      <c r="N8" s="150"/>
+      <c r="N8" s="149"/>
       <c r="O8">
         <v>12</v>
       </c>
@@ -9774,7 +9772,7 @@
       <c r="L9" s="105">
         <v>801417.68719647545</v>
       </c>
-      <c r="N9" s="150"/>
+      <c r="N9" s="149"/>
       <c r="O9">
         <v>11</v>
       </c>
@@ -9831,7 +9829,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L10" s="110"/>
-      <c r="N10" s="150"/>
+      <c r="N10" s="149"/>
       <c r="O10">
         <v>8</v>
       </c>
@@ -9894,7 +9892,7 @@
       <c r="L11" s="103">
         <v>473999.33273359912</v>
       </c>
-      <c r="N11" s="150"/>
+      <c r="N11" s="149"/>
       <c r="O11">
         <v>52</v>
       </c>
@@ -9955,7 +9953,7 @@
       <c r="L12" s="105">
         <v>0</v>
       </c>
-      <c r="N12" s="150"/>
+      <c r="N12" s="149"/>
       <c r="O12">
         <v>53</v>
       </c>
@@ -10016,7 +10014,7 @@
       <c r="L13" s="105">
         <v>1774250.1300302623</v>
       </c>
-      <c r="N13" s="150"/>
+      <c r="N13" s="149"/>
       <c r="O13">
         <v>5</v>
       </c>
@@ -10077,7 +10075,7 @@
       <c r="L14" s="105">
         <v>688681.10694474855</v>
       </c>
-      <c r="N14" s="150"/>
+      <c r="N14" s="149"/>
       <c r="O14">
         <v>4</v>
       </c>
@@ -10138,7 +10136,7 @@
       <c r="L15" s="105">
         <v>542644.60453174426</v>
       </c>
-      <c r="N15" s="151"/>
+      <c r="N15" s="150"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="23"/>
       <c r="R15" s="14"/>
@@ -10184,7 +10182,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L16" s="110"/>
-      <c r="N16" s="149" t="s">
+      <c r="N16" s="148" t="s">
         <v>38</v>
       </c>
       <c r="O16">
@@ -10249,7 +10247,7 @@
       <c r="L17" s="103">
         <v>0</v>
       </c>
-      <c r="N17" s="150"/>
+      <c r="N17" s="149"/>
       <c r="O17">
         <v>54</v>
       </c>
@@ -10310,7 +10308,7 @@
       <c r="L18" s="105">
         <v>0</v>
       </c>
-      <c r="N18" s="150"/>
+      <c r="N18" s="149"/>
       <c r="O18">
         <v>21</v>
       </c>
@@ -10371,7 +10369,7 @@
       <c r="L19" s="105">
         <v>0</v>
       </c>
-      <c r="N19" s="150"/>
+      <c r="N19" s="149"/>
       <c r="O19">
         <v>23</v>
       </c>
@@ -10432,7 +10430,7 @@
       <c r="L20" s="105">
         <v>532961.24250140926</v>
       </c>
-      <c r="N20" s="150"/>
+      <c r="N20" s="149"/>
       <c r="O20">
         <v>18</v>
       </c>
@@ -10493,7 +10491,7 @@
       <c r="L21" s="105">
         <v>243114.33850570052</v>
       </c>
-      <c r="N21" s="150"/>
+      <c r="N21" s="149"/>
       <c r="O21">
         <v>44</v>
       </c>
@@ -10554,7 +10552,7 @@
       <c r="L22" s="105">
         <v>399885.11500273226</v>
       </c>
-      <c r="N22" s="150"/>
+      <c r="N22" s="149"/>
       <c r="O22">
         <v>56</v>
       </c>
@@ -10615,7 +10613,7 @@
       <c r="L23" s="105">
         <v>0</v>
       </c>
-      <c r="N23" s="150"/>
+      <c r="N23" s="149"/>
       <c r="O23">
         <v>2</v>
       </c>
@@ -10676,7 +10674,7 @@
       <c r="L24" s="105">
         <v>532480.47978304385</v>
       </c>
-      <c r="N24" s="150"/>
+      <c r="N24" s="149"/>
       <c r="O24">
         <v>3</v>
       </c>
@@ -10737,7 +10735,7 @@
       <c r="L25" s="105">
         <v>855398.40214226511</v>
       </c>
-      <c r="N25" s="151"/>
+      <c r="N25" s="150"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="23"/>
       <c r="R25" s="14"/>
@@ -10783,7 +10781,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="L26" s="110"/>
-      <c r="N26" s="149" t="s">
+      <c r="N26" s="148" t="s">
         <v>221</v>
       </c>
       <c r="O26">
@@ -10848,7 +10846,7 @@
       <c r="L27" s="103">
         <v>0</v>
       </c>
-      <c r="N27" s="150"/>
+      <c r="N27" s="149"/>
       <c r="O27">
         <v>36</v>
       </c>
@@ -10909,7 +10907,7 @@
       <c r="L28" s="105">
         <v>0</v>
       </c>
-      <c r="N28" s="150"/>
+      <c r="N28" s="149"/>
       <c r="O28">
         <v>9</v>
       </c>
@@ -10970,7 +10968,7 @@
       <c r="L29" s="105">
         <v>0</v>
       </c>
-      <c r="N29" s="150"/>
+      <c r="N29" s="149"/>
       <c r="O29">
         <v>40</v>
       </c>
@@ -11031,7 +11029,7 @@
       <c r="L30" s="105">
         <v>0</v>
       </c>
-      <c r="N30" s="150"/>
+      <c r="N30" s="149"/>
       <c r="O30">
         <v>27</v>
       </c>
@@ -11092,7 +11090,7 @@
       <c r="L31" s="105">
         <v>245173.74682820804</v>
       </c>
-      <c r="N31" s="150"/>
+      <c r="N31" s="149"/>
       <c r="O31">
         <v>10</v>
       </c>
@@ -11153,7 +11151,7 @@
       <c r="L32" s="105">
         <v>0</v>
       </c>
-      <c r="N32" s="150"/>
+      <c r="N32" s="149"/>
       <c r="O32">
         <v>28</v>
       </c>
@@ -11214,7 +11212,7 @@
       <c r="L33" s="105">
         <v>0</v>
       </c>
-      <c r="N33" s="150"/>
+      <c r="N33" s="149"/>
       <c r="O33">
         <v>33</v>
       </c>
@@ -11275,7 +11273,7 @@
       <c r="L34" s="105">
         <v>0</v>
       </c>
-      <c r="N34" s="150"/>
+      <c r="N34" s="149"/>
       <c r="O34">
         <v>37</v>
       </c>
@@ -11336,7 +11334,7 @@
       <c r="L35" s="105">
         <v>0</v>
       </c>
-      <c r="N35" s="150"/>
+      <c r="N35" s="149"/>
       <c r="O35">
         <v>24</v>
       </c>
@@ -11397,7 +11395,7 @@
       <c r="L36" s="105">
         <v>0</v>
       </c>
-      <c r="N36" s="150"/>
+      <c r="N36" s="149"/>
       <c r="O36">
         <v>7</v>
       </c>
@@ -11458,7 +11456,7 @@
       <c r="L37" s="105">
         <v>0</v>
       </c>
-      <c r="N37" s="150"/>
+      <c r="N37" s="149"/>
       <c r="O37">
         <v>57</v>
       </c>
@@ -11519,7 +11517,7 @@
       <c r="L38" s="105">
         <v>0</v>
       </c>
-      <c r="N38" s="150"/>
+      <c r="N38" s="149"/>
       <c r="O38">
         <v>1</v>
       </c>
@@ -11580,7 +11578,7 @@
       <c r="L39" s="105">
         <v>0</v>
       </c>
-      <c r="N39" s="151"/>
+      <c r="N39" s="150"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="23"/>
       <c r="R39" s="14"/>
@@ -13626,7 +13624,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="142" t="s">
         <v>206</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -13670,7 +13668,7 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144"/>
+      <c r="A3" s="143"/>
       <c r="B3" s="36" t="s">
         <v>93</v>
       </c>
@@ -13712,7 +13710,7 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="144"/>
+      <c r="A4" s="143"/>
       <c r="B4" s="36" t="s">
         <v>91</v>
       </c>
@@ -13754,7 +13752,7 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="144"/>
+      <c r="A5" s="143"/>
       <c r="B5" s="36" t="s">
         <v>89</v>
       </c>
@@ -13790,7 +13788,7 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="144"/>
+      <c r="A6" s="143"/>
       <c r="B6" s="36" t="s">
         <v>209</v>
       </c>
@@ -13826,7 +13824,7 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="144"/>
+      <c r="A7" s="143"/>
       <c r="B7" s="36" t="s">
         <v>269</v>
       </c>
@@ -13862,7 +13860,7 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="144"/>
+      <c r="A8" s="143"/>
       <c r="B8" s="36" t="s">
         <v>84</v>
       </c>
@@ -13898,7 +13896,7 @@
       </c>
     </row>
     <row r="9" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="143"/>
       <c r="B9" s="36" t="s">
         <v>83</v>
       </c>
@@ -13934,7 +13932,7 @@
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="145"/>
+      <c r="A10" s="144"/>
       <c r="B10" s="3"/>
       <c r="C10" s="64">
         <v>242974591.73925051</v>
@@ -13966,7 +13964,7 @@
       <c r="L10" s="67"/>
     </row>
     <row r="11" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="142" t="s">
         <v>207</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -14004,7 +14002,7 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="144"/>
+      <c r="A12" s="143"/>
       <c r="B12" s="36" t="s">
         <v>90</v>
       </c>
@@ -14046,7 +14044,7 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="144"/>
+      <c r="A13" s="143"/>
       <c r="B13" s="36" t="s">
         <v>270</v>
       </c>
@@ -14083,7 +14081,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+      <c r="A14" s="143"/>
       <c r="B14" s="36" t="s">
         <v>107</v>
       </c>
@@ -14119,7 +14117,7 @@
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="145"/>
+      <c r="A15" s="144"/>
       <c r="B15" s="3"/>
       <c r="C15" s="64">
         <v>341864881.75327951</v>
@@ -14151,7 +14149,7 @@
       <c r="L15" s="67"/>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="145" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="68" t="s">
@@ -14189,7 +14187,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="147"/>
+      <c r="A17" s="146"/>
       <c r="B17" s="19" t="s">
         <v>82</v>
       </c>
@@ -14225,7 +14223,7 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="147"/>
+      <c r="A18" s="146"/>
       <c r="B18" s="19" t="s">
         <v>92</v>
       </c>
@@ -14261,7 +14259,7 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="147"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="19" t="s">
         <v>95</v>
       </c>
@@ -14297,7 +14295,7 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="147"/>
+      <c r="A20" s="146"/>
       <c r="B20" s="19" t="s">
         <v>97</v>
       </c>
@@ -14333,7 +14331,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="147"/>
+      <c r="A21" s="146"/>
       <c r="B21" s="19" t="s">
         <v>218</v>
       </c>
@@ -14369,7 +14367,7 @@
       </c>
     </row>
     <row r="22" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="147"/>
+      <c r="A22" s="146"/>
       <c r="B22" s="19" t="s">
         <v>160</v>
       </c>
@@ -14405,7 +14403,7 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="147"/>
+      <c r="A23" s="146"/>
       <c r="B23" s="19" t="s">
         <v>219</v>
       </c>
@@ -14441,7 +14439,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="148"/>
+      <c r="A24" s="147"/>
       <c r="B24" s="71"/>
       <c r="C24" s="66">
         <v>237630000</v>
@@ -14473,7 +14471,7 @@
       <c r="L24" s="67"/>
     </row>
     <row r="25" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="143" t="s">
+      <c r="A25" s="142" t="s">
         <v>216</v>
       </c>
       <c r="B25" s="57" t="s">
@@ -14511,7 +14509,7 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="144"/>
+      <c r="A26" s="143"/>
       <c r="B26" s="36" t="s">
         <v>213</v>
       </c>
@@ -14547,7 +14545,7 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="144"/>
+      <c r="A27" s="143"/>
       <c r="B27" s="36" t="s">
         <v>86</v>
       </c>
@@ -14584,7 +14582,7 @@
       <c r="M27" s="27"/>
     </row>
     <row r="28" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="144"/>
+      <c r="A28" s="143"/>
       <c r="B28" s="36" t="s">
         <v>212</v>
       </c>
@@ -14621,7 +14619,7 @@
       <c r="M28" s="26"/>
     </row>
     <row r="29" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="144"/>
+      <c r="A29" s="143"/>
       <c r="B29" s="36" t="s">
         <v>98</v>
       </c>
@@ -14658,7 +14656,7 @@
       <c r="M29" s="27"/>
     </row>
     <row r="30" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="144"/>
+      <c r="A30" s="143"/>
       <c r="B30" s="36" t="s">
         <v>210</v>
       </c>
@@ -14695,7 +14693,7 @@
       <c r="M30" s="26"/>
     </row>
     <row r="31" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="144"/>
+      <c r="A31" s="143"/>
       <c r="B31" s="36" t="s">
         <v>99</v>
       </c>
@@ -14731,7 +14729,7 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="144"/>
+      <c r="A32" s="143"/>
       <c r="B32" s="36" t="s">
         <v>138</v>
       </c>
@@ -14767,7 +14765,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="144"/>
+      <c r="A33" s="143"/>
       <c r="B33" s="19" t="s">
         <v>272</v>
       </c>
@@ -14803,7 +14801,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="144"/>
+      <c r="A34" s="143"/>
       <c r="B34" s="36" t="s">
         <v>274</v>
       </c>
@@ -14839,7 +14837,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="144"/>
+      <c r="A35" s="143"/>
       <c r="B35" s="36" t="s">
         <v>110</v>
       </c>
@@ -14875,7 +14873,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="144"/>
+      <c r="A36" s="143"/>
       <c r="B36" s="36" t="s">
         <v>214</v>
       </c>
@@ -14911,7 +14909,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="144"/>
+      <c r="A37" s="143"/>
       <c r="B37" s="36" t="s">
         <v>80</v>
       </c>
@@ -14947,7 +14945,7 @@
       </c>
     </row>
     <row r="38" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="145"/>
+      <c r="A38" s="144"/>
       <c r="B38" s="3"/>
       <c r="C38" s="74">
         <v>521754707.42240375</v>
@@ -14979,7 +14977,7 @@
       <c r="L38" s="67"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="143" t="s">
+      <c r="A39" s="142" t="s">
         <v>264</v>
       </c>
       <c r="B39" s="136" t="s">
@@ -15017,7 +15015,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="144"/>
+      <c r="A40" s="143"/>
       <c r="B40" s="136" t="s">
         <v>145</v>
       </c>
@@ -15053,7 +15051,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="144"/>
+      <c r="A41" s="143"/>
       <c r="B41" s="136" t="s">
         <v>106</v>
       </c>
@@ -15089,7 +15087,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="144"/>
+      <c r="A42" s="143"/>
       <c r="B42" s="137" t="s">
         <v>139</v>
       </c>
@@ -15125,7 +15123,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="144"/>
+      <c r="A43" s="143"/>
       <c r="B43" s="138" t="s">
         <v>265</v>
       </c>
@@ -15161,7 +15159,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="144"/>
+      <c r="A44" s="143"/>
       <c r="B44" s="138" t="s">
         <v>266</v>
       </c>
@@ -15197,7 +15195,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="144"/>
+      <c r="A45" s="143"/>
       <c r="B45" s="138" t="s">
         <v>273</v>
       </c>
@@ -15233,7 +15231,7 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="144"/>
+      <c r="A46" s="143"/>
       <c r="B46" s="138" t="s">
         <v>267</v>
       </c>
@@ -15269,7 +15267,7 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="145"/>
+      <c r="A47" s="144"/>
       <c r="B47" s="135"/>
       <c r="C47" s="66">
         <v>455695855.27356702</v>
@@ -15399,7 +15397,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -15415,10 +15413,9 @@
     <col min="11" max="11" width="17.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.42578125" style="142" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
         <v>205</v>
       </c>
@@ -15456,8 +15453,8 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="143" t="s">
+    <row r="2" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="142" t="s">
         <v>206</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -15507,13 +15504,9 @@
       <c r="N2">
         <v>21</v>
       </c>
-      <c r="P2" s="142">
-        <f>+C2*1.02</f>
-        <v>33583151.334436089</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="144"/>
+    </row>
+    <row r="3" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="143"/>
       <c r="B3" s="36" t="s">
         <v>93</v>
       </c>
@@ -15562,13 +15555,9 @@
         <f>N4-N2</f>
         <v>4</v>
       </c>
-      <c r="P3" s="142">
-        <f t="shared" ref="P3:P23" si="6">+C3*1.02</f>
-        <v>32234430.397310141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="144"/>
+    </row>
+    <row r="4" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="143"/>
       <c r="B4" s="36" t="s">
         <v>91</v>
       </c>
@@ -15616,13 +15605,9 @@
       <c r="N4">
         <v>25</v>
       </c>
-      <c r="P4" s="142">
-        <f t="shared" si="6"/>
-        <v>29536988.523058243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="144"/>
+    </row>
+    <row r="5" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="143"/>
       <c r="B5" s="36" t="s">
         <v>89</v>
       </c>
@@ -15664,13 +15649,9 @@
         <f t="array" ref="L5">+_xlfn.IFS(I5&gt;114%,H5*0.02,I5&gt;109%,H5*0.015,I5&gt;104%,H5*0.0125,I5&gt;99%,H5*0.01,I5&lt;99%,H5*0)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="142">
-        <f t="shared" si="6"/>
-        <v>29536988.523058243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="144"/>
+    </row>
+    <row r="6" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="143"/>
       <c r="B6" s="36" t="s">
         <v>209</v>
       </c>
@@ -15712,13 +15693,9 @@
         <f t="array" ref="L6">+_xlfn.IFS(I6&gt;114%,H6*0.02,I6&gt;109%,H6*0.015,I6&gt;104%,H6*0.0125,I6&gt;99%,H6*0.01,I6&lt;99%,H6*0)</f>
         <v>0</v>
       </c>
-      <c r="P6" s="142">
-        <f t="shared" si="6"/>
-        <v>24479285.008835938</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="144"/>
+    </row>
+    <row r="7" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="143"/>
       <c r="B7" s="36" t="s">
         <v>269</v>
       </c>
@@ -15760,13 +15737,9 @@
         <f t="array" ref="L7">+_xlfn.IFS(I7&gt;114%,H7*0.02,I7&gt;109%,H7*0.015,I7&gt;104%,H7*0.0125,I7&gt;99%,H7*0.01,I7&lt;99%,H7*0)</f>
         <v>0</v>
       </c>
-      <c r="P7" s="142">
-        <f t="shared" si="6"/>
-        <v>28862628.054495271</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="144"/>
+    </row>
+    <row r="8" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="143"/>
       <c r="B8" s="36" t="s">
         <v>84</v>
       </c>
@@ -15808,13 +15781,9 @@
         <f t="array" ref="L8">+_xlfn.IFS(I8&gt;114%,H8*0.02,I8&gt;109%,H8*0.015,I8&gt;104%,H8*0.0125,I8&gt;99%,H8*0.01,I8&lt;99%,H8*0)</f>
         <v>0</v>
       </c>
-      <c r="P8" s="142">
-        <f t="shared" si="6"/>
-        <v>37278646.702161185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="143"/>
       <c r="B9" s="36" t="s">
         <v>83</v>
       </c>
@@ -15856,13 +15825,9 @@
         <f t="array" ref="L9">+_xlfn.IFS(I9&gt;114%,H9*0.02,I9&gt;109%,H9*0.015,I9&gt;104%,H9*0.0125,I9&gt;99%,H9*0.01,I9&lt;99%,H9*0)</f>
         <v>599341.13817489217</v>
       </c>
-      <c r="P9" s="142">
-        <f t="shared" si="6"/>
-        <v>37278646.702161185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="145"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="144"/>
       <c r="B10" s="3"/>
       <c r="C10" s="64">
         <v>247834083.57403553</v>
@@ -15899,13 +15864,9 @@
         <v>10018627.205718648</v>
       </c>
       <c r="L10" s="67"/>
-      <c r="P10" s="142">
-        <f t="shared" si="6"/>
-        <v>252790765.24551624</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="143" t="s">
+    </row>
+    <row r="11" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="142" t="s">
         <v>207</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -15922,7 +15883,7 @@
         <v>15952320.537641706</v>
       </c>
       <c r="F11" s="59">
-        <f t="shared" ref="F11:F14" si="7">+D11-E11</f>
+        <f t="shared" ref="F11:F14" si="6">+D11-E11</f>
         <v>3857651.4751310069</v>
       </c>
       <c r="G11" s="60">
@@ -15949,13 +15910,9 @@
         <f t="array" ref="L11">+_xlfn.IFS(I11&gt;114%,H11*0.0125,I11&gt;109%,H11*0.01,I11&gt;104%,H11*0.0075,I11&gt;99%,H11*0.005,I11&lt;99%,H11*0)</f>
         <v>1547654.0634978684</v>
       </c>
-      <c r="P11" s="142">
-        <f t="shared" si="6"/>
-        <v>100889615.19873507</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="144"/>
+    </row>
+    <row r="12" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="143"/>
       <c r="B12" s="36" t="s">
         <v>90</v>
       </c>
@@ -15970,7 +15927,7 @@
         <v>10658290.360380379</v>
       </c>
       <c r="F12" s="59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1453856.5993695613</v>
       </c>
       <c r="G12" s="5">
@@ -16003,13 +15960,9 @@
       <c r="N12" s="25">
         <v>0.02</v>
       </c>
-      <c r="P12" s="142">
-        <f t="shared" si="6"/>
-        <v>133549818.28403984</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="144"/>
+    </row>
+    <row r="13" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="143"/>
       <c r="B13" s="36" t="s">
         <v>270</v>
       </c>
@@ -16024,7 +15977,7 @@
         <v>9198857.9277629387</v>
       </c>
       <c r="F13" s="59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>1343948.10984</v>
       </c>
       <c r="G13" s="5">
@@ -16052,13 +16005,9 @@
         <v>988388.06602527539</v>
       </c>
       <c r="N13" s="28"/>
-      <c r="P13" s="142">
-        <f t="shared" si="6"/>
-        <v>44163999.313731991</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="143"/>
       <c r="B14" s="36" t="s">
         <v>107</v>
       </c>
@@ -16073,7 +16022,7 @@
         <v>6609956.6165299807</v>
       </c>
       <c r="F14" s="59">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>183552.80019999947</v>
       </c>
       <c r="G14" s="5">
@@ -16100,13 +16049,9 @@
         <f t="array" ref="L14">+_xlfn.IFS(I14&gt;109%,H14*0.015,I14&gt;104%,H14*0.0125,I14&gt;99%,H14*0.01,I14&lt;99%,H14*0)</f>
         <v>0</v>
       </c>
-      <c r="P14" s="142">
-        <f t="shared" si="6"/>
-        <v>44163999.313731991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="145"/>
+    </row>
+    <row r="15" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="144"/>
       <c r="B15" s="3"/>
       <c r="C15" s="64">
         <v>348702179.38834512</v>
@@ -16143,14 +16088,10 @@
         <v>14259225.950547121</v>
       </c>
       <c r="L15" s="67"/>
-      <c r="P15" s="142">
-        <f t="shared" si="6"/>
-        <v>355676222.97611201</v>
-      </c>
-      <c r="Q15" s="27"/>
-    </row>
-    <row r="16" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="146" t="s">
+      <c r="P15" s="27"/>
+    </row>
+    <row r="16" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="145" t="s">
         <v>208</v>
       </c>
       <c r="B16" s="68" t="s">
@@ -16167,7 +16108,7 @@
         <v>2005760.5287147206</v>
       </c>
       <c r="F16" s="59">
-        <f t="shared" ref="F16:F46" si="8">+D16-E16</f>
+        <f t="shared" ref="F16:F46" si="7">+D16-E16</f>
         <v>922196.67594530154</v>
       </c>
       <c r="G16" s="60">
@@ -16194,13 +16135,9 @@
         <f t="array" ref="L16">+_xlfn.IFS(I16&gt;114%,H16*0.02,I16&gt;109%,H16*0.015,I16&gt;104%,H16*0.0125,I16&gt;99%,H16*0.01,I16&lt;99%,H16*0)</f>
         <v>0</v>
       </c>
-      <c r="P16" s="142">
-        <f t="shared" si="6"/>
-        <v>29578572</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="147"/>
+    </row>
+    <row r="17" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="146"/>
       <c r="B17" s="19" t="s">
         <v>82</v>
       </c>
@@ -16215,7 +16152,7 @@
         <v>2539763.9949347642</v>
       </c>
       <c r="F17" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>2092163.6297328467</v>
       </c>
       <c r="G17" s="5">
@@ -16242,13 +16179,9 @@
         <f t="array" ref="L17">+_xlfn.IFS(I17&gt;114%,H17*0.02,I17&gt;109%,H17*0.015,I17&gt;104%,H17*0.0125,I17&gt;99%,H17*0.01,I17&lt;99%,H17*0)</f>
         <v>434243.21481258853</v>
       </c>
-      <c r="P17" s="142">
-        <f t="shared" si="6"/>
-        <v>26010000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="147"/>
+    </row>
+    <row r="18" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="146"/>
       <c r="B18" s="19" t="s">
         <v>92</v>
       </c>
@@ -16263,7 +16196,7 @@
         <v>2809522.8802084369</v>
       </c>
       <c r="F18" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>830673.700067495</v>
       </c>
       <c r="G18" s="5">
@@ -16290,13 +16223,9 @@
         <f t="array" ref="L18">+_xlfn.IFS(I18&gt;114%,H18*0.02,I18&gt;109%,H18*0.015,I18&gt;104%,H18*0.0125,I18&gt;99%,H18*0.01,I18&lt;99%,H18*0)</f>
         <v>0</v>
       </c>
-      <c r="P18" s="142">
-        <f t="shared" si="6"/>
-        <v>26530200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="147"/>
+    </row>
+    <row r="19" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="146"/>
       <c r="B19" s="19" t="s">
         <v>95</v>
       </c>
@@ -16311,7 +16240,7 @@
         <v>4496479.3262617178</v>
       </c>
       <c r="F19" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1789259.9968198417</v>
       </c>
       <c r="G19" s="5">
@@ -16338,13 +16267,9 @@
         <f t="array" ref="L19">+_xlfn.IFS(I19&gt;114%,H19*0.02,I19&gt;109%,H19*0.015,I19&gt;104%,H19*0.0125,I19&gt;99%,H19*0.01,I19&lt;99%,H19*0)</f>
         <v>589288.06153889617</v>
       </c>
-      <c r="P19" s="142">
-        <f t="shared" si="6"/>
-        <v>36622080</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="147"/>
+    </row>
+    <row r="20" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="146"/>
       <c r="B20" s="19" t="s">
         <v>97</v>
       </c>
@@ -16359,7 +16284,7 @@
         <v>2639381.27863609</v>
       </c>
       <c r="F20" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>860461.74245218886</v>
       </c>
       <c r="G20" s="5">
@@ -16386,13 +16311,9 @@
         <f t="array" ref="L20">+_xlfn.IFS(I20&gt;114%,H20*0.02,I20&gt;109%,H20*0.015,I20&gt;104%,H20*0.0125,I20&gt;99%,H20*0.01,I20&lt;99%,H20*0)</f>
         <v>0</v>
       </c>
-      <c r="P20" s="142">
-        <f t="shared" si="6"/>
-        <v>27154440</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="147"/>
+    </row>
+    <row r="21" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="146"/>
       <c r="B21" s="19" t="s">
         <v>218</v>
       </c>
@@ -16407,7 +16328,7 @@
         <v>3344638.0010631969</v>
       </c>
       <c r="F21" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>553240.02883539302</v>
       </c>
       <c r="G21" s="5">
@@ -16434,13 +16355,9 @@
         <f t="array" ref="L21">+_xlfn.IFS(I21&gt;114%,H21*0.02,I21&gt;109%,H21*0.015,I21&gt;104%,H21*0.0125,I21&gt;99%,H21*0.01,I21&lt;99%,H21*0)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="142">
-        <f t="shared" si="6"/>
-        <v>33917040</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="147"/>
+    </row>
+    <row r="22" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="146"/>
       <c r="B22" s="19" t="s">
         <v>160</v>
       </c>
@@ -16455,7 +16372,7 @@
         <v>1765164.2460201115</v>
       </c>
       <c r="F22" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>780794.55074598012</v>
       </c>
       <c r="G22" s="5">
@@ -16482,13 +16399,9 @@
         <f t="array" ref="L22">+_xlfn.IFS(I22&gt;114%,H22*0.02,I22&gt;109%,H22*0.015,I22&gt;104%,H22*0.0125,I22&gt;99%,H22*0.01,I22&lt;99%,H22*0)</f>
         <v>0</v>
       </c>
-      <c r="P22" s="142">
-        <f t="shared" si="6"/>
-        <v>29339280</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="147"/>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="146"/>
       <c r="B23" s="19" t="s">
         <v>219</v>
       </c>
@@ -16503,7 +16416,7 @@
         <v>2716546.2402552781</v>
       </c>
       <c r="F23" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>544518.58524148399</v>
       </c>
       <c r="G23" s="5">
@@ -16530,13 +16443,9 @@
         <f t="array" ref="L23">+_xlfn.IFS(I23&gt;114%,H23*0.02,I23&gt;109%,H23*0.015,I23&gt;104%,H23*0.0125,I23&gt;99%,H23*0.01,I23&lt;99%,H23*0)</f>
         <v>0</v>
       </c>
-      <c r="P23" s="142">
-        <f t="shared" si="6"/>
-        <v>38078640</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="148"/>
+    </row>
+    <row r="24" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="147"/>
       <c r="B24" s="71"/>
       <c r="C24" s="66">
         <v>242382600</v>
@@ -16573,13 +16482,9 @@
         <v>10080573.075907866</v>
       </c>
       <c r="L24" s="67"/>
-      <c r="P24" s="142">
-        <f t="shared" ref="P24" si="9">+C24*1.02</f>
-        <v>247230252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="143" t="s">
+    </row>
+    <row r="25" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="142" t="s">
         <v>216</v>
       </c>
       <c r="B25" s="57" t="s">
@@ -16596,7 +16501,7 @@
         <v>3813088.6969673904</v>
       </c>
       <c r="F25" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1013478.9456474287</v>
       </c>
       <c r="G25" s="60">
@@ -16623,12 +16528,9 @@
         <f t="array" ref="L25">+_xlfn.IFS(I25&gt;114%,H25*0.0125,I25&gt;109%,H25*0.01,I25&gt;104%,H25*0.0075,I25&gt;99%,H25*0.005,I25&lt;99%,H25*0)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="142">
-        <v>86547956.260000005</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="144"/>
+    </row>
+    <row r="26" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="143"/>
       <c r="B26" s="36" t="s">
         <v>213</v>
       </c>
@@ -16643,7 +16545,7 @@
         <v>1882261.6002979665</v>
       </c>
       <c r="F26" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>988300.62442020606</v>
       </c>
       <c r="G26" s="5">
@@ -16670,12 +16572,9 @@
         <f t="array" ref="L26">+_xlfn.IFS(I26&gt;114%,H26*0.02,I26&gt;109%,H26*0.015,I26&gt;104%,H26*0.0125,I26&gt;99%,H26*0.01,I26&lt;99%,H26*0)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="142">
-        <v>24010803.390000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="144"/>
+    </row>
+    <row r="27" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="143"/>
       <c r="B27" s="36" t="s">
         <v>86</v>
       </c>
@@ -16690,7 +16589,7 @@
         <v>2138310.9760203827</v>
       </c>
       <c r="F27" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>783739.78934368957</v>
       </c>
       <c r="G27" s="5">
@@ -16718,12 +16617,9 @@
         <v>0</v>
       </c>
       <c r="M27" s="27"/>
-      <c r="P27" s="142">
-        <v>26910856.350000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="144"/>
+    </row>
+    <row r="28" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="143"/>
       <c r="B28" s="36" t="s">
         <v>212</v>
       </c>
@@ -16738,7 +16634,7 @@
         <v>2561364.7764617526</v>
       </c>
       <c r="F28" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1326264.6427335185</v>
       </c>
       <c r="G28" s="5">
@@ -16766,12 +16662,9 @@
         <v>0</v>
       </c>
       <c r="M28" s="26"/>
-      <c r="P28" s="142">
-        <v>39189035</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="144"/>
+    </row>
+    <row r="29" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="143"/>
       <c r="B29" s="36" t="s">
         <v>98</v>
       </c>
@@ -16786,7 +16679,7 @@
         <v>1166677.533230609</v>
       </c>
       <c r="F29" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1168536.1154567541</v>
       </c>
       <c r="G29" s="5">
@@ -16814,12 +16707,9 @@
         <v>0</v>
       </c>
       <c r="M29" s="27"/>
-      <c r="P29" s="142">
-        <v>26900000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="144"/>
+    </row>
+    <row r="30" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="143"/>
       <c r="B30" s="36" t="s">
         <v>210</v>
       </c>
@@ -16834,7 +16724,7 @@
         <v>1515047.2062076211</v>
       </c>
       <c r="F30" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>943057.97292957432</v>
       </c>
       <c r="G30" s="5">
@@ -16862,12 +16752,9 @@
         <v>0</v>
       </c>
       <c r="M30" s="26"/>
-      <c r="P30" s="142">
-        <v>25830000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="144"/>
+    </row>
+    <row r="31" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="143"/>
       <c r="B31" s="36" t="s">
         <v>99</v>
       </c>
@@ -16882,7 +16769,7 @@
         <v>1531376.1832633617</v>
       </c>
       <c r="F31" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>984294.24050668557</v>
       </c>
       <c r="G31" s="5">
@@ -16909,12 +16796,9 @@
         <f t="array" ref="L31">+_xlfn.IFS(I31&gt;114%,H31*0.02,I31&gt;109%,H31*0.015,I31&gt;104%,H31*0.0125,I31&gt;99%,H31*0.01,I31&lt;99%,H31*0)</f>
         <v>0</v>
       </c>
-      <c r="P31" s="142">
-        <v>27702000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="144"/>
+    </row>
+    <row r="32" spans="1:13" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="143"/>
       <c r="B32" s="36" t="s">
         <v>138</v>
       </c>
@@ -16929,7 +16813,7 @@
         <v>1155215.0172623193</v>
       </c>
       <c r="F32" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>618626.68510555802</v>
       </c>
       <c r="G32" s="5">
@@ -16956,12 +16840,9 @@
         <f t="array" ref="L32">+_xlfn.IFS(I32&gt;114%,H32*0.02,I32&gt;109%,H32*0.015,I32&gt;104%,H32*0.0125,I32&gt;99%,H32*0.01,I32&lt;99%,H32*0)</f>
         <v>0</v>
       </c>
-      <c r="P32" s="142">
-        <v>24010803.390000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="144"/>
+    </row>
+    <row r="33" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="143"/>
       <c r="B33" s="19" t="s">
         <v>272</v>
       </c>
@@ -16976,7 +16857,7 @@
         <v>1831514.0723396542</v>
       </c>
       <c r="F33" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>620985.22149805515</v>
       </c>
       <c r="G33" s="5">
@@ -17003,12 +16884,9 @@
         <f t="array" ref="L33">+_xlfn.IFS(I33&gt;114%,H33*0.02,I33&gt;109%,H33*0.015,I33&gt;104%,H33*0.0125,I33&gt;99%,H33*0.01,I33&lt;99%,H33*0)</f>
         <v>0</v>
       </c>
-      <c r="P33" s="142">
-        <v>25780148</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="144"/>
+    </row>
+    <row r="34" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="143"/>
       <c r="B34" s="36" t="s">
         <v>274</v>
       </c>
@@ -17023,7 +16901,7 @@
         <v>2209452.8796649785</v>
       </c>
       <c r="F34" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>975649.62310678931</v>
       </c>
       <c r="G34" s="5">
@@ -17050,12 +16928,9 @@
         <f t="array" ref="L34">+_xlfn.IFS(I34&gt;114%,H34*0.02,I34&gt;109%,H34*0.015,I34&gt;104%,H34*0.0125,I34&gt;99%,H34*0.01,I34&lt;99%,H34*0)</f>
         <v>0</v>
       </c>
-      <c r="P34" s="142">
-        <v>26383192</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="144"/>
+    </row>
+    <row r="35" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="143"/>
       <c r="B35" s="36" t="s">
         <v>110</v>
       </c>
@@ -17070,7 +16945,7 @@
         <v>13251421.94303805</v>
       </c>
       <c r="F35" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>595519.34999999963</v>
       </c>
       <c r="G35" s="5">
@@ -17097,12 +16972,9 @@
         <f t="array" ref="L35">+_xlfn.IFS(I35&gt;114%,H35*0.0125,I35&gt;109%,H35*0.01,I35&gt;104%,H35*0.0075,I35&gt;99%,H35*0.005,I35&lt;99%,H35*0)</f>
         <v>0</v>
       </c>
-      <c r="P35" s="142">
-        <v>125062043.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="144"/>
+    </row>
+    <row r="36" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="143"/>
       <c r="B36" s="36" t="s">
         <v>284</v>
       </c>
@@ -17117,7 +16989,7 @@
         <v>4904802.4244999997</v>
       </c>
       <c r="F36" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1209982.1323000006</v>
       </c>
       <c r="G36" s="5">
@@ -17144,12 +17016,9 @@
         <f t="array" ref="L36">+_xlfn.IFS(I36&gt;109%,H36*0.015,I36&gt;104%,H36*0.0125,I36&gt;99%,H36*0.01,I36&lt;99%,H36*0)</f>
         <v>477717.54350000009</v>
       </c>
-      <c r="P36" s="142">
-        <v>36592500</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="144"/>
+    </row>
+    <row r="37" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="143"/>
       <c r="B37" s="36" t="s">
         <v>80</v>
       </c>
@@ -17164,7 +17033,7 @@
         <v>3309540.3255070136</v>
       </c>
       <c r="F37" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1160707.5421055802</v>
       </c>
       <c r="G37" s="5">
@@ -17191,12 +17060,9 @@
         <f t="array" ref="L37">+_xlfn.IFS(I37&gt;114%,H37*0.02,I37&gt;109%,H37*0.015,I37&gt;104%,H37*0.0125,I37&gt;99%,H37*0.01,I37&lt;99%,H37*0)</f>
         <v>0</v>
       </c>
-      <c r="P37" s="142">
-        <v>37270463.43</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="145"/>
+    </row>
+    <row r="38" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="144"/>
       <c r="B38" s="3"/>
       <c r="C38" s="74">
         <v>532189801.57085186</v>
@@ -17233,13 +17099,9 @@
         <v>22787170.716711283</v>
       </c>
       <c r="L38" s="67"/>
-      <c r="P38" s="142">
-        <f t="shared" ref="P38" si="10">+C38*1.02</f>
-        <v>542833597.60226893</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="143" t="s">
+    </row>
+    <row r="39" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="142" t="s">
         <v>264</v>
       </c>
       <c r="B39" s="136" t="s">
@@ -17256,7 +17118,7 @@
         <v>2871011.5105904969</v>
       </c>
       <c r="F39" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-23475.871999999974</v>
       </c>
       <c r="G39" s="5">
@@ -17264,32 +17126,28 @@
         <v>8.1358161102585633E-2</v>
       </c>
       <c r="H39" s="4">
-        <f t="shared" ref="H39:H47" si="11">+D39/$N$3*$N$4</f>
+        <f t="shared" ref="H39:H47" si="8">+D39/$N$3*$N$4</f>
         <v>17797097.741190605</v>
       </c>
       <c r="I39" s="5">
-        <f t="shared" ref="I39:I47" si="12">+H39/C39</f>
+        <f t="shared" ref="I39:I47" si="9">+H39/C39</f>
         <v>0.5084885068911601</v>
       </c>
       <c r="J39" s="4">
-        <f t="shared" ref="J39:J47" si="13">+D39/$N$3</f>
+        <f t="shared" ref="J39:J47" si="10">+D39/$N$3</f>
         <v>711883.90964762424</v>
       </c>
       <c r="K39" s="4">
-        <f t="shared" ref="K39:K47" si="14">+(C39-D39)/$N$2</f>
+        <f t="shared" ref="K39:K47" si="11">+(C39-D39)/$N$2</f>
         <v>1531069.7314956908</v>
       </c>
       <c r="L39" s="63" cm="1">
         <f t="array" ref="L39">+_xlfn.IFS(I39&gt;114%,H39*0.02,I39&gt;109%,H39*0.015,I39&gt;104%,H39*0.0125,I39&gt;99%,H39*0.01,I39&lt;99%,H39*0)</f>
         <v>0</v>
       </c>
-      <c r="P39" s="142">
-        <f>+C39</f>
-        <v>35000000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="144"/>
+    </row>
+    <row r="40" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="143"/>
       <c r="B40" s="136" t="s">
         <v>145</v>
       </c>
@@ -17304,7 +17162,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-80990.517827873206</v>
       </c>
       <c r="G40" s="5">
@@ -17312,32 +17170,28 @@
         <v>-2.6996839275957737E-3</v>
       </c>
       <c r="H40" s="4">
+        <f t="shared" si="8"/>
+        <v>-506190.73642420751</v>
+      </c>
+      <c r="I40" s="5">
+        <f t="shared" si="9"/>
+        <v>-1.6873024547473584E-2</v>
+      </c>
+      <c r="J40" s="4">
+        <f t="shared" si="10"/>
+        <v>-20247.629456968301</v>
+      </c>
+      <c r="K40" s="4">
         <f t="shared" si="11"/>
-        <v>-506190.73642420751</v>
-      </c>
-      <c r="I40" s="5">
-        <f t="shared" si="12"/>
-        <v>-1.6873024547473584E-2</v>
-      </c>
-      <c r="J40" s="4">
-        <f t="shared" si="13"/>
-        <v>-20247.629456968301</v>
-      </c>
-      <c r="K40" s="4">
-        <f t="shared" si="14"/>
         <v>1432428.1198965653</v>
       </c>
       <c r="L40" s="63" cm="1">
         <f t="array" ref="L40">+_xlfn.IFS(I40&gt;114%,H40*0.02,I40&gt;109%,H40*0.015,I40&gt;104%,H40*0.0125,I40&gt;99%,H40*0.01,I40&lt;99%,H40*0)</f>
         <v>0</v>
       </c>
-      <c r="P40" s="142">
-        <f>+C40</f>
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="144"/>
+    </row>
+    <row r="41" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="143"/>
       <c r="B41" s="136" t="s">
         <v>106</v>
       </c>
@@ -17352,7 +17206,7 @@
         <v>10831777.123155374</v>
       </c>
       <c r="F41" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>-456146.24543135427</v>
       </c>
       <c r="G41" s="5">
@@ -17360,32 +17214,28 @@
         <v>0.32002143281353329</v>
       </c>
       <c r="H41" s="4">
+        <f t="shared" si="8"/>
+        <v>64847692.985775121</v>
+      </c>
+      <c r="I41" s="5">
+        <f t="shared" si="9"/>
+        <v>2.0001339550845829</v>
+      </c>
+      <c r="J41" s="4">
+        <f t="shared" si="10"/>
+        <v>2593907.719431005</v>
+      </c>
+      <c r="K41" s="4">
         <f t="shared" si="11"/>
-        <v>64847692.985775121</v>
-      </c>
-      <c r="I41" s="5">
-        <f t="shared" si="12"/>
-        <v>2.0001339550845829</v>
-      </c>
-      <c r="J41" s="4">
-        <f t="shared" si="13"/>
-        <v>2593907.719431005</v>
-      </c>
-      <c r="K41" s="4">
-        <f t="shared" si="14"/>
         <v>1049811.6233836743</v>
       </c>
       <c r="L41" s="63" cm="1">
         <f t="array" ref="L41">+_xlfn.IFS(I41&gt;114%,H41*0.02,I41&gt;109%,H41*0.015,I41&gt;104%,H41*0.0125,I41&gt;99%,H41*0.01,I41&lt;99%,H41*0)</f>
         <v>1296953.8597155025</v>
       </c>
-      <c r="P41" s="142">
-        <f>+C41</f>
-        <v>32421674.968781177</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="144"/>
+    </row>
+    <row r="42" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="143"/>
       <c r="B42" s="137" t="s">
         <v>139</v>
       </c>
@@ -17400,7 +17250,7 @@
         <v>3672776.0578550007</v>
       </c>
       <c r="F42" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>18032753.065169558</v>
       </c>
       <c r="G42" s="5">
@@ -17408,32 +17258,28 @@
         <v>0.38399936959485925</v>
       </c>
       <c r="H42" s="4">
+        <f t="shared" si="8"/>
+        <v>135659557.01890349</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="9"/>
+        <v>2.39999605996787</v>
+      </c>
+      <c r="J42" s="4">
+        <f t="shared" si="10"/>
+        <v>5426382.2807561401</v>
+      </c>
+      <c r="K42" s="4">
         <f t="shared" si="11"/>
-        <v>135659557.01890349</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" si="12"/>
-        <v>2.39999605996787</v>
-      </c>
-      <c r="J42" s="4">
-        <f t="shared" si="13"/>
-        <v>5426382.2807561401</v>
-      </c>
-      <c r="K42" s="4">
-        <f t="shared" si="14"/>
         <v>1658065.6713015689</v>
       </c>
       <c r="L42" s="63" cm="1">
         <f t="array" ref="L42">+_xlfn.IFS(I42&gt;114%,H42*0.02,I42&gt;109%,H42*0.015,I42&gt;104%,H42*0.0125,I42&gt;99%,H42*0.01,I42&lt;99%,H42*0)</f>
         <v>2713191.1403780701</v>
       </c>
-      <c r="P42" s="142">
-        <f>+C42*1.02</f>
-        <v>57655406.384764656</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="144"/>
+    </row>
+    <row r="43" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="143"/>
       <c r="B43" s="138" t="s">
         <v>265</v>
       </c>
@@ -17448,7 +17294,7 @@
         <v>22371341.880147766</v>
       </c>
       <c r="F43" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1730556.7877499983</v>
       </c>
       <c r="G43" s="5">
@@ -17456,32 +17302,28 @@
         <v>0.24101898667897764</v>
       </c>
       <c r="H43" s="4">
+        <f t="shared" si="8"/>
+        <v>150636866.67436102</v>
+      </c>
+      <c r="I43" s="5">
+        <f t="shared" si="9"/>
+        <v>1.5063686667436103</v>
+      </c>
+      <c r="J43" s="4">
+        <f t="shared" si="10"/>
+        <v>6025474.6669744411</v>
+      </c>
+      <c r="K43" s="4">
         <f t="shared" si="11"/>
-        <v>150636866.67436102</v>
-      </c>
-      <c r="I43" s="5">
-        <f t="shared" si="12"/>
-        <v>1.5063686667436103</v>
-      </c>
-      <c r="J43" s="4">
-        <f t="shared" si="13"/>
-        <v>6025474.6669744411</v>
-      </c>
-      <c r="K43" s="4">
-        <f t="shared" si="14"/>
         <v>3614195.3015286783</v>
       </c>
       <c r="L43" s="63" cm="1">
         <f t="array" ref="L43">+_xlfn.IFS(I43&gt;114%,H43*0.02,I43&gt;109%,H43*0.015,I43&gt;104%,H43*0.0125,I43&gt;99%,H43*0.01,I43&lt;99%,H43*0)</f>
         <v>3012737.3334872206</v>
       </c>
-      <c r="P43" s="142">
-        <f t="shared" ref="P43:P46" si="15">+C43</f>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="144"/>
+    </row>
+    <row r="44" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="143"/>
       <c r="B44" s="138" t="s">
         <v>266</v>
       </c>
@@ -17496,7 +17338,7 @@
         <v>2923678.1117493762</v>
       </c>
       <c r="F44" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G44" s="5">
@@ -17504,32 +17346,28 @@
         <v>2.9236781117493761E-2</v>
       </c>
       <c r="H44" s="4">
+        <f t="shared" si="8"/>
+        <v>18272988.1984336</v>
+      </c>
+      <c r="I44" s="5">
+        <f t="shared" si="9"/>
+        <v>0.18272988198433601</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" si="10"/>
+        <v>730919.52793734404</v>
+      </c>
+      <c r="K44" s="4">
         <f t="shared" si="11"/>
-        <v>18272988.1984336</v>
-      </c>
-      <c r="I44" s="5">
-        <f t="shared" si="12"/>
-        <v>0.18272988198433601</v>
-      </c>
-      <c r="J44" s="4">
-        <f t="shared" si="13"/>
-        <v>730919.52793734404</v>
-      </c>
-      <c r="K44" s="4">
-        <f t="shared" si="14"/>
         <v>4622681.9946786007</v>
       </c>
       <c r="L44" s="63" cm="1">
         <f t="array" ref="L44">+_xlfn.IFS(I44&gt;114%,H44*0.02,I44&gt;109%,H44*0.015,I44&gt;104%,H44*0.0125,I44&gt;99%,H44*0.01,I44&lt;99%,H44*0)</f>
         <v>0</v>
       </c>
-      <c r="P44" s="142">
-        <f t="shared" si="15"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="144"/>
+    </row>
+    <row r="45" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="143"/>
       <c r="B45" s="138" t="s">
         <v>273</v>
       </c>
@@ -17544,7 +17382,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>7269845.9948500441</v>
       </c>
       <c r="G45" s="5">
@@ -17552,32 +17390,28 @@
         <v>0.29079383979400175</v>
       </c>
       <c r="H45" s="4">
+        <f t="shared" si="8"/>
+        <v>45436537.467812777</v>
+      </c>
+      <c r="I45" s="5">
+        <f t="shared" si="9"/>
+        <v>1.8174614987125111</v>
+      </c>
+      <c r="J45" s="4">
+        <f t="shared" si="10"/>
+        <v>1817461.498712511</v>
+      </c>
+      <c r="K45" s="4">
         <f t="shared" si="11"/>
-        <v>45436537.467812777</v>
-      </c>
-      <c r="I45" s="5">
-        <f t="shared" si="12"/>
-        <v>1.8174614987125111</v>
-      </c>
-      <c r="J45" s="4">
-        <f t="shared" si="13"/>
-        <v>1817461.498712511</v>
-      </c>
-      <c r="K45" s="4">
-        <f t="shared" si="14"/>
         <v>844293.04786428367</v>
       </c>
       <c r="L45" s="63" cm="1">
         <f t="array" ref="L45">+_xlfn.IFS(I45&gt;114%,H45*0.02,I45&gt;109%,H45*0.015,I45&gt;104%,H45*0.0125,I45&gt;99%,H45*0.01,I45&lt;99%,H45*0)</f>
         <v>908730.74935625552</v>
       </c>
-      <c r="P45" s="142">
-        <f t="shared" si="15"/>
-        <v>25000000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="144"/>
+    </row>
+    <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A46" s="143"/>
       <c r="B46" s="138" t="s">
         <v>267</v>
       </c>
@@ -17592,7 +17426,7 @@
         <v>3242995.6574940565</v>
       </c>
       <c r="F46" s="59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G46" s="5">
@@ -17600,32 +17434,28 @@
         <v>3.2429956574940563E-2</v>
       </c>
       <c r="H46" s="4">
+        <f t="shared" si="8"/>
+        <v>20268722.859337851</v>
+      </c>
+      <c r="I46" s="5">
+        <f t="shared" si="9"/>
+        <v>0.20268722859337851</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="10"/>
+        <v>810748.91437351413</v>
+      </c>
+      <c r="K46" s="4">
         <f t="shared" si="11"/>
-        <v>20268722.859337851</v>
-      </c>
-      <c r="I46" s="5">
-        <f t="shared" si="12"/>
-        <v>0.20268722859337851</v>
-      </c>
-      <c r="J46" s="4">
-        <f t="shared" si="13"/>
-        <v>810748.91437351413</v>
-      </c>
-      <c r="K46" s="4">
-        <f t="shared" si="14"/>
         <v>4607476.3972621877</v>
       </c>
       <c r="L46" s="63" cm="1">
         <f t="array" ref="L46">+_xlfn.IFS(I46&gt;114%,H46*0.02,I46&gt;109%,H46*0.015,I46&gt;104%,H46*0.0125,I46&gt;99%,H46*0.01,I46&lt;99%,H46*0)</f>
         <v>0</v>
       </c>
-      <c r="P46" s="142">
-        <f t="shared" si="15"/>
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="145"/>
+    </row>
+    <row r="47" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="144"/>
       <c r="B47" s="135"/>
       <c r="C47" s="66">
         <v>478946583.18913865</v>
@@ -17646,28 +17476,24 @@
         <v>0.15113611015138353</v>
       </c>
       <c r="H47" s="64">
+        <f t="shared" si="8"/>
+        <v>452413272.20939028</v>
+      </c>
+      <c r="I47" s="65">
+        <f t="shared" si="9"/>
+        <v>0.9446006884461472</v>
+      </c>
+      <c r="J47" s="64">
+        <f t="shared" si="10"/>
+        <v>18096530.88837561</v>
+      </c>
+      <c r="K47" s="66">
         <f t="shared" si="11"/>
-        <v>452413272.20939028</v>
-      </c>
-      <c r="I47" s="65">
-        <f t="shared" si="12"/>
-        <v>0.9446006884461472</v>
-      </c>
-      <c r="J47" s="64">
-        <f t="shared" si="13"/>
-        <v>18096530.88837561</v>
-      </c>
-      <c r="K47" s="66">
-        <f t="shared" si="14"/>
         <v>19360021.887411248</v>
       </c>
       <c r="L47" s="67"/>
-      <c r="P47" s="142">
-        <f>SUM(P39:P46)</f>
-        <v>480077081.35354584</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:12" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="75" t="s">
         <v>271</v>
       </c>
@@ -17707,10 +17533,6 @@
         <v>76505618.836296156</v>
       </c>
       <c r="L48" s="79"/>
-      <c r="P48" s="142">
-        <f>+P10+P15+P24+P38+P47</f>
-        <v>1878607919.177443</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -18521,7 +18343,7 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="149" t="s">
+      <c r="A15" s="148" t="s">
         <v>38</v>
       </c>
       <c r="B15">
@@ -18562,7 +18384,7 @@
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="150"/>
+      <c r="A16" s="149"/>
       <c r="B16">
         <v>54</v>
       </c>
@@ -18601,7 +18423,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="150"/>
+      <c r="A17" s="149"/>
       <c r="B17">
         <v>21</v>
       </c>
@@ -18640,7 +18462,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="150"/>
+      <c r="A18" s="149"/>
       <c r="B18">
         <v>23</v>
       </c>
@@ -18679,7 +18501,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="150"/>
+      <c r="A19" s="149"/>
       <c r="B19">
         <v>18</v>
       </c>
@@ -18718,7 +18540,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="150"/>
+      <c r="A20" s="149"/>
       <c r="B20">
         <v>44</v>
       </c>
@@ -18757,7 +18579,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="150"/>
+      <c r="A21" s="149"/>
       <c r="B21">
         <v>2</v>
       </c>
@@ -18796,7 +18618,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="150"/>
+      <c r="A22" s="149"/>
       <c r="B22">
         <v>3</v>
       </c>
@@ -18835,7 +18657,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="151"/>
+      <c r="A23" s="150"/>
       <c r="C23" s="9"/>
       <c r="D23" s="23"/>
       <c r="E23" s="14"/>
@@ -18854,7 +18676,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="149" t="s">
+      <c r="A24" s="148" t="s">
         <v>215</v>
       </c>
       <c r="B24">
@@ -18895,7 +18717,7 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="150"/>
+      <c r="A25" s="149"/>
       <c r="B25">
         <v>36</v>
       </c>
@@ -18934,7 +18756,7 @@
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="150"/>
+      <c r="A26" s="149"/>
       <c r="B26">
         <v>9</v>
       </c>
@@ -18973,7 +18795,7 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="150"/>
+      <c r="A27" s="149"/>
       <c r="B27">
         <v>40</v>
       </c>
@@ -19012,7 +18834,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="150"/>
+      <c r="A28" s="149"/>
       <c r="B28">
         <v>27</v>
       </c>
@@ -19051,7 +18873,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="150"/>
+      <c r="A29" s="149"/>
       <c r="B29">
         <v>10</v>
       </c>
@@ -19090,7 +18912,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="150"/>
+      <c r="A30" s="149"/>
       <c r="B30">
         <v>28</v>
       </c>
@@ -19129,7 +18951,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="150"/>
+      <c r="A31" s="149"/>
       <c r="B31">
         <v>33</v>
       </c>
@@ -19168,7 +18990,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="150"/>
+      <c r="A32" s="149"/>
       <c r="B32">
         <v>37</v>
       </c>
@@ -19207,7 +19029,7 @@
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="150"/>
+      <c r="A33" s="149"/>
       <c r="B33">
         <v>24</v>
       </c>
@@ -19246,7 +19068,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="150"/>
+      <c r="A34" s="149"/>
       <c r="B34">
         <v>7</v>
       </c>
@@ -19282,7 +19104,7 @@
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="150"/>
+      <c r="A35" s="149"/>
       <c r="B35">
         <v>57</v>
       </c>
@@ -19318,7 +19140,7 @@
       </c>
     </row>
     <row r="36" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="150"/>
+      <c r="A36" s="149"/>
       <c r="B36">
         <v>1</v>
       </c>
@@ -19357,7 +19179,7 @@
       </c>
     </row>
     <row r="37" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="151"/>
+      <c r="A37" s="150"/>
       <c r="C37" s="9"/>
       <c r="D37" s="23"/>
       <c r="E37" s="14"/>
@@ -19376,7 +19198,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="149" t="s">
+      <c r="A38" s="148" t="s">
         <v>268</v>
       </c>
       <c r="B38">
@@ -19411,7 +19233,7 @@
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="150"/>
+      <c r="A39" s="149"/>
       <c r="B39">
         <v>59</v>
       </c>
@@ -19444,7 +19266,7 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="150"/>
+      <c r="A40" s="149"/>
       <c r="B40">
         <v>49</v>
       </c>
@@ -19477,7 +19299,7 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="150"/>
+      <c r="A41" s="149"/>
       <c r="B41">
         <v>56</v>
       </c>
@@ -19510,7 +19332,7 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="150"/>
+      <c r="A42" s="149"/>
       <c r="B42">
         <v>26</v>
       </c>
@@ -19543,7 +19365,7 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="150"/>
+      <c r="A43" s="149"/>
       <c r="B43">
         <v>25</v>
       </c>
@@ -19576,7 +19398,7 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="150"/>
+      <c r="A44" s="149"/>
       <c r="B44">
         <v>60</v>
       </c>
@@ -19609,7 +19431,7 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="150"/>
+      <c r="A45" s="149"/>
       <c r="B45">
         <v>43</v>
       </c>
